--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27260" windowHeight="11920"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="地形地貌" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -50,8 +50,8 @@
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -81,16 +81,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -104,9 +103,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -141,11 +148,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -157,8 +171,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -174,14 +189,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -195,31 +203,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,181 +240,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,6 +458,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -473,11 +482,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,6 +512,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -511,185 +546,150 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27260" windowHeight="11920"/>
+    <workbookView windowWidth="27260" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="地形地貌" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10">
   <si>
     <t>段落</t>
   </si>
@@ -22,25 +22,50 @@
     <t>地形</t>
   </si>
   <si>
-    <t>最高海拔</t>
+    <t>最高海拔（m）</t>
   </si>
   <si>
-    <t>最低海拔</t>
+    <t>最低海拔（m）</t>
   </si>
   <si>
-    <t>高差</t>
+    <t>高差（m）</t>
+  </si>
+  <si>
+    <t>高填/深挖</t>
   </si>
   <si>
     <t>位置</t>
   </si>
   <si>
-    <t>坡率</t>
+    <r>
+      <t>坡率（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
   </si>
   <si>
     <t>类型</t>
   </si>
   <si>
-    <t>最大填高/挖深</t>
+    <t>最大填高/挖深（m）</t>
   </si>
 </sst>
 </file>
@@ -48,12 +73,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -69,6 +94,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="方正书宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -103,6 +135,84 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -117,79 +227,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -203,8 +242,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,11 +258,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -252,19 +291,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,139 +411,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,16 +474,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -454,15 +493,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -478,45 +508,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -546,164 +537,221 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1025,10 +1073,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="10" width="16.7211538461538" customWidth="1"/>
+    <col min="1" max="9" width="16.7211538461538" customWidth="1"/>
+    <col min="10" max="10" width="21.6346153846154" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1038,44 +1087,69 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="14" customHeight="1" spans="1:10">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+  </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTerrainLandforms.xlsx
@@ -38,6 +38,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
       <t>坡率（</t>
     </r>
     <r>
@@ -73,9 +80,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
@@ -106,27 +113,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -135,15 +121,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,6 +165,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -165,9 +211,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -175,15 +227,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,28 +236,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,30 +250,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,13 +286,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,169 +466,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,8 +498,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,59 +571,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,152 +597,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -746,12 +753,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1112,19 +1113,19 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1150,6 +1151,11 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="G$1:G$1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
